--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Area.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Area.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sala</t>
+          <t>Cômodo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Espaço onde os moradores vivem</t>
+          <t>居民的生活空间</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Mudar-se</t>
+          <t>Alocar</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sala Privada</t>
+          <t>Quarto Privativo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Espaço onde os moradores vivem</t>
+          <t>居民的生活空间</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mudar-se</t>
+          <t>Alocar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Depósito</t>
+          <t>Estoque</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Local para cultivar e colher plantações</t>
+          <t>培育和收获作物的场所</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Local para criar animais de fazenda</t>
+          <t>培育家畜的场所</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Pastorear</t>
+          <t>Pastar</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prisão</t>
+          <t>Cadeia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sala de Estar</t>
+          <t>Sala de Visitas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
